--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/164.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/164.xlsx
@@ -426,13 +426,13 @@
         <v>-13.13233300268642</v>
       </c>
       <c r="E2">
-        <v>-5.393577644907274</v>
+        <v>-3.973978027560747</v>
       </c>
       <c r="F2">
-        <v>-3.66102906230901</v>
+        <v>-3.722565539359326</v>
       </c>
       <c r="G2">
-        <v>-12.62147588241297</v>
+        <v>-10.77537333625717</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.78020575785369</v>
       </c>
       <c r="E3">
-        <v>-6.115203563451568</v>
+        <v>-4.989053590276089</v>
       </c>
       <c r="F3">
-        <v>-3.545344888156863</v>
+        <v>-3.846231591325288</v>
       </c>
       <c r="G3">
-        <v>-12.27416986043357</v>
+        <v>-10.90745086109193</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.32281519080899</v>
       </c>
       <c r="E4">
-        <v>-6.521298998563415</v>
+        <v>-6.534567427405889</v>
       </c>
       <c r="F4">
-        <v>-3.411131354794074</v>
+        <v>-3.805286458587517</v>
       </c>
       <c r="G4">
-        <v>-11.58832083051722</v>
+        <v>-10.18066693558249</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.79395089256768</v>
       </c>
       <c r="E5">
-        <v>-7.300572391225353</v>
+        <v>-5.499263171298285</v>
       </c>
       <c r="F5">
-        <v>-3.388614224088356</v>
+        <v>-3.531274452951141</v>
       </c>
       <c r="G5">
-        <v>-11.40529069928753</v>
+        <v>-9.623376320592659</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.18979286530592</v>
       </c>
       <c r="E6">
-        <v>-8.393650918722816</v>
+        <v>-7.017465781687826</v>
       </c>
       <c r="F6">
-        <v>-3.109983340149601</v>
+        <v>-3.588172255375135</v>
       </c>
       <c r="G6">
-        <v>-10.75133546509652</v>
+        <v>-9.067065627082449</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.53145622903454</v>
       </c>
       <c r="E7">
-        <v>-8.647191121464264</v>
+        <v>-7.624824715596574</v>
       </c>
       <c r="F7">
-        <v>-3.2831354508553</v>
+        <v>-3.757705598064054</v>
       </c>
       <c r="G7">
-        <v>-10.874073940965</v>
+        <v>-9.847023535043663</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.816267651644342</v>
       </c>
       <c r="E8">
-        <v>-9.437600031711064</v>
+        <v>-8.96008150455024</v>
       </c>
       <c r="F8">
-        <v>-3.345494663128686</v>
+        <v>-3.577406222561977</v>
       </c>
       <c r="G8">
-        <v>-10.32579463093306</v>
+        <v>-9.806704400920879</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.068540902223502</v>
       </c>
       <c r="E9">
-        <v>-9.817452959948461</v>
+        <v>-8.929215425713959</v>
       </c>
       <c r="F9">
-        <v>-3.230184243572582</v>
+        <v>-3.524957050054453</v>
       </c>
       <c r="G9">
-        <v>-9.732640876116305</v>
+        <v>-8.469733963795132</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.296914375897266</v>
       </c>
       <c r="E10">
-        <v>-9.92053914225907</v>
+        <v>-11.09263954119038</v>
       </c>
       <c r="F10">
-        <v>-3.546143867791202</v>
+        <v>-3.970360085418559</v>
       </c>
       <c r="G10">
-        <v>-9.514058796340384</v>
+        <v>-7.961273895509549</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.515929983516686</v>
       </c>
       <c r="E11">
-        <v>-12.49546116233849</v>
+        <v>-11.84074797573153</v>
       </c>
       <c r="F11">
-        <v>-3.342579060538362</v>
+        <v>-3.556935239899007</v>
       </c>
       <c r="G11">
-        <v>-8.905507694220477</v>
+        <v>-7.853578538571518</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.750215348788577</v>
       </c>
       <c r="E12">
-        <v>-12.19309948132035</v>
+        <v>-12.3541320170331</v>
       </c>
       <c r="F12">
-        <v>-3.307500766364336</v>
+        <v>-3.903614799612364</v>
       </c>
       <c r="G12">
-        <v>-8.713959529318245</v>
+        <v>-7.473693437940149</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.010907705396817</v>
       </c>
       <c r="E13">
-        <v>-13.59414594065745</v>
+        <v>-12.9464654741844</v>
       </c>
       <c r="F13">
-        <v>-3.081404575052539</v>
+        <v>-3.343287768935521</v>
       </c>
       <c r="G13">
-        <v>-8.096863909161479</v>
+        <v>-7.439200863966482</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.331370656218696</v>
       </c>
       <c r="E14">
-        <v>-14.59191820418948</v>
+        <v>-13.42927325898619</v>
       </c>
       <c r="F14">
-        <v>-3.174427501260663</v>
+        <v>-3.369837014901948</v>
       </c>
       <c r="G14">
-        <v>-8.032980311890162</v>
+        <v>-6.416080075600261</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.734301891071246</v>
       </c>
       <c r="E15">
-        <v>-14.95825363751398</v>
+        <v>-12.81727716769358</v>
       </c>
       <c r="F15">
-        <v>-3.146805294536526</v>
+        <v>-3.150107321370217</v>
       </c>
       <c r="G15">
-        <v>-8.281489723341092</v>
+        <v>-6.380011681949902</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.242783366386384</v>
       </c>
       <c r="E16">
-        <v>-16.07376622524544</v>
+        <v>-15.13132285713913</v>
       </c>
       <c r="F16">
-        <v>-2.557832191261215</v>
+        <v>-3.14214365617443</v>
       </c>
       <c r="G16">
-        <v>-6.993435907103617</v>
+        <v>-6.596852414772164</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.890250074787952</v>
       </c>
       <c r="E17">
-        <v>-17.43347224536652</v>
+        <v>-16.25514066620066</v>
       </c>
       <c r="F17">
-        <v>-2.41703677611386</v>
+        <v>-2.84113025653277</v>
       </c>
       <c r="G17">
-        <v>-6.968957733386246</v>
+        <v>-5.636105614911352</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.689076731384012</v>
       </c>
       <c r="E18">
-        <v>-16.57831521375805</v>
+        <v>-16.34601355411258</v>
       </c>
       <c r="F18">
-        <v>-2.265206098147722</v>
+        <v>-2.762354348739938</v>
       </c>
       <c r="G18">
-        <v>-5.650797816014637</v>
+        <v>-4.903498439798335</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.661509806505991</v>
       </c>
       <c r="E19">
-        <v>-18.87967664750811</v>
+        <v>-17.11708135187262</v>
       </c>
       <c r="F19">
-        <v>-1.701414710780856</v>
+        <v>-2.348162989557314</v>
       </c>
       <c r="G19">
-        <v>-6.223873112135715</v>
+        <v>-5.123086925418193</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.806688055102336</v>
       </c>
       <c r="E20">
-        <v>-17.90586001147665</v>
+        <v>-17.95546944423068</v>
       </c>
       <c r="F20">
-        <v>-1.680771104173103</v>
+        <v>-1.980831112853669</v>
       </c>
       <c r="G20">
-        <v>-5.697847289218759</v>
+        <v>-4.855330002201939</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.107217402717959</v>
       </c>
       <c r="E21">
-        <v>-19.04535086907873</v>
+        <v>-19.06550257841286</v>
       </c>
       <c r="F21">
-        <v>-1.374932152607099</v>
+        <v>-1.60766644726346</v>
       </c>
       <c r="G21">
-        <v>-6.273514742497087</v>
+        <v>-5.574582436609536</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.541006176796666</v>
       </c>
       <c r="E22">
-        <v>-20.68940882908945</v>
+        <v>-19.74640845868019</v>
       </c>
       <c r="F22">
-        <v>-1.043578906890407</v>
+        <v>-1.257878072838096</v>
       </c>
       <c r="G22">
-        <v>-5.826448741237288</v>
+        <v>-5.212527934252682</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.059483363342403</v>
       </c>
       <c r="E23">
-        <v>-20.7189571219895</v>
+        <v>-19.49602007384808</v>
       </c>
       <c r="F23">
-        <v>-0.7153368514445961</v>
+        <v>-1.248979229299241</v>
       </c>
       <c r="G23">
-        <v>-6.557175526483999</v>
+        <v>-4.521842197303456</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.623339394990272</v>
       </c>
       <c r="E24">
-        <v>-20.10026794611356</v>
+        <v>-19.15903368056729</v>
       </c>
       <c r="F24">
-        <v>-0.8360033644067163</v>
+        <v>-1.09233329349721</v>
       </c>
       <c r="G24">
-        <v>-6.570023753721911</v>
+        <v>-5.092394857723609</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.18882305118685</v>
       </c>
       <c r="E25">
-        <v>-20.91576007388884</v>
+        <v>-20.23080120938465</v>
       </c>
       <c r="F25">
-        <v>-0.7486437705522032</v>
+        <v>-1.217174455252429</v>
       </c>
       <c r="G25">
-        <v>-6.585404548297364</v>
+        <v>-4.921087368248482</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.716343834721227</v>
       </c>
       <c r="E26">
-        <v>-20.39830946292838</v>
+        <v>-19.92013883551045</v>
       </c>
       <c r="F26">
-        <v>-0.5723978903406934</v>
+        <v>-0.8727785994691357</v>
       </c>
       <c r="G26">
-        <v>-7.478576492610574</v>
+        <v>-5.938477602286225</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.182596656742392</v>
       </c>
       <c r="E27">
-        <v>-20.94800733729747</v>
+        <v>-19.46799334821461</v>
       </c>
       <c r="F27">
-        <v>-0.6033054949864096</v>
+        <v>-1.007989867558652</v>
       </c>
       <c r="G27">
-        <v>-7.632854535831689</v>
+        <v>-7.06214959031673</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.560839393939258</v>
       </c>
       <c r="E28">
-        <v>-20.46009596228904</v>
+        <v>-20.43467763768398</v>
       </c>
       <c r="F28">
-        <v>-0.6021715615509551</v>
+        <v>-0.927655593145028</v>
       </c>
       <c r="G28">
-        <v>-7.837270791245068</v>
+        <v>-6.605271132078531</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.838965202674107</v>
       </c>
       <c r="E29">
-        <v>-20.84976209370106</v>
+        <v>-20.78437998597831</v>
       </c>
       <c r="F29">
-        <v>-0.5525817700737573</v>
+        <v>-0.800970997704238</v>
       </c>
       <c r="G29">
-        <v>-7.76866966658029</v>
+        <v>-6.499625002829309</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.006333974908477</v>
       </c>
       <c r="E30">
-        <v>-20.37115673277839</v>
+        <v>-19.94471486395008</v>
       </c>
       <c r="F30">
-        <v>-0.3633732569443757</v>
+        <v>-0.9362677859131877</v>
       </c>
       <c r="G30">
-        <v>-7.940344626610276</v>
+        <v>-6.350081039729351</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.053689728259704</v>
       </c>
       <c r="E31">
-        <v>-21.10502764503942</v>
+        <v>-19.63426079988023</v>
       </c>
       <c r="F31">
-        <v>-0.3863805446309223</v>
+        <v>-0.6341806336608594</v>
       </c>
       <c r="G31">
-        <v>-7.798226217154903</v>
+        <v>-7.111890537044279</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.982643653348762</v>
       </c>
       <c r="E32">
-        <v>-19.68338115744143</v>
+        <v>-18.82947851313309</v>
       </c>
       <c r="F32">
-        <v>-0.4450552650920383</v>
+        <v>-0.627070585953494</v>
       </c>
       <c r="G32">
-        <v>-7.083297355221594</v>
+        <v>-6.691630023015959</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.791800817202111</v>
       </c>
       <c r="E33">
-        <v>-19.44660989395039</v>
+        <v>-18.1897409900695</v>
       </c>
       <c r="F33">
-        <v>-0.3013284102952044</v>
+        <v>-0.7092063258459301</v>
       </c>
       <c r="G33">
-        <v>-7.560648227074646</v>
+        <v>-6.060222914492923</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.490429091557166</v>
       </c>
       <c r="E34">
-        <v>-20.24193219849551</v>
+        <v>-18.62015885907654</v>
       </c>
       <c r="F34">
-        <v>-0.3559884362606815</v>
+        <v>-0.7444382394937538</v>
       </c>
       <c r="G34">
-        <v>-7.019370720858268</v>
+        <v>-7.011408858836321</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.091724306015732</v>
       </c>
       <c r="E35">
-        <v>-19.27002657849529</v>
+        <v>-17.79017561447671</v>
       </c>
       <c r="F35">
-        <v>-0.4657170843178191</v>
+        <v>-0.7139542761804175</v>
       </c>
       <c r="G35">
-        <v>-6.725245302421719</v>
+        <v>-6.91529379019466</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.609363037903354</v>
       </c>
       <c r="E36">
-        <v>-18.6119894919667</v>
+        <v>-18.23190561155491</v>
       </c>
       <c r="F36">
-        <v>-0.2352308602084237</v>
+        <v>-0.4487698473167016</v>
       </c>
       <c r="G36">
-        <v>-6.719246593904559</v>
+        <v>-4.916899528141304</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.068837475023102</v>
       </c>
       <c r="E37">
-        <v>-18.11276598888712</v>
+        <v>-17.60842078170485</v>
       </c>
       <c r="F37">
-        <v>-0.658018575100054</v>
+        <v>-0.6366789297424651</v>
       </c>
       <c r="G37">
-        <v>-6.127393883484735</v>
+        <v>-5.823346760066991</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.489838790797205</v>
       </c>
       <c r="E38">
-        <v>-17.53915324328353</v>
+        <v>-17.52184994410022</v>
       </c>
       <c r="F38">
-        <v>-0.4793733804266535</v>
+        <v>-0.7725355579925227</v>
       </c>
       <c r="G38">
-        <v>-5.674547669713369</v>
+        <v>-5.560290811516502</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.897390285484321</v>
       </c>
       <c r="E39">
-        <v>-17.75549203205196</v>
+        <v>-16.83137086978068</v>
       </c>
       <c r="F39">
-        <v>-0.5180878633825284</v>
+        <v>-0.4297661681843859</v>
       </c>
       <c r="G39">
-        <v>-6.050334314967119</v>
+        <v>-5.146270675829708</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.315521248373671</v>
       </c>
       <c r="E40">
-        <v>-17.39165178790569</v>
+        <v>-16.07447266719064</v>
       </c>
       <c r="F40">
-        <v>-0.4110546827934689</v>
+        <v>-0.5723654243694269</v>
       </c>
       <c r="G40">
-        <v>-5.761409763572766</v>
+        <v>-4.142632447962098</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.760195468614599</v>
       </c>
       <c r="E41">
-        <v>-17.0000565265664</v>
+        <v>-15.39691332921499</v>
       </c>
       <c r="F41">
-        <v>-0.3948311993957072</v>
+        <v>-0.6748153600392047</v>
       </c>
       <c r="G41">
-        <v>-6.089229914508017</v>
+        <v>-4.046775601872501</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.254705593391225</v>
       </c>
       <c r="E42">
-        <v>-17.69673508180244</v>
+        <v>-15.27349429860994</v>
       </c>
       <c r="F42">
-        <v>-0.3323840914440143</v>
+        <v>-0.8976419904885773</v>
       </c>
       <c r="G42">
-        <v>-5.78083273425167</v>
+        <v>-4.291438159406799</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.810101708088856</v>
       </c>
       <c r="E43">
-        <v>-17.08095318623942</v>
+        <v>-15.32689406410839</v>
       </c>
       <c r="F43">
-        <v>-0.7029340585678322</v>
+        <v>-0.6499258378721584</v>
       </c>
       <c r="G43">
-        <v>-5.14090428151055</v>
+        <v>-5.276133445698699</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.438301148629133</v>
       </c>
       <c r="E44">
-        <v>-15.77243250782704</v>
+        <v>-14.18565068706534</v>
       </c>
       <c r="F44">
-        <v>-0.468726125557154</v>
+        <v>-1.385860515276588</v>
       </c>
       <c r="G44">
-        <v>-5.32891016268576</v>
+        <v>-4.944185044475978</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.147981573071743</v>
       </c>
       <c r="E45">
-        <v>-15.40182672351331</v>
+        <v>-13.16137326516641</v>
       </c>
       <c r="F45">
-        <v>-0.706573414761512</v>
+        <v>-0.9678833071031054</v>
       </c>
       <c r="G45">
-        <v>-5.434778098486114</v>
+        <v>-4.173503285115802</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.935823024347168</v>
       </c>
       <c r="E46">
-        <v>-15.1032644321876</v>
+        <v>-13.04608284540513</v>
       </c>
       <c r="F46">
-        <v>-1.087060344651755</v>
+        <v>-0.9884556469446638</v>
       </c>
       <c r="G46">
-        <v>-5.189748070396957</v>
+        <v>-4.195227084944499</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.804667115351462</v>
       </c>
       <c r="E47">
-        <v>-14.78571877782174</v>
+        <v>-12.81062936785032</v>
       </c>
       <c r="F47">
-        <v>-0.8259286192256482</v>
+        <v>-1.566828214674981</v>
       </c>
       <c r="G47">
-        <v>-5.153871688387875</v>
+        <v>-4.022724488529696</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.744766720766695</v>
       </c>
       <c r="E48">
-        <v>-13.4186539874382</v>
+        <v>-12.35025111480853</v>
       </c>
       <c r="F48">
-        <v>-0.7249594485868063</v>
+        <v>-1.219795488542481</v>
       </c>
       <c r="G48">
-        <v>-5.130870017981019</v>
+        <v>-4.329827245480187</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.748571695908666</v>
       </c>
       <c r="E49">
-        <v>-14.0534373599374</v>
+        <v>-12.11871023879634</v>
       </c>
       <c r="F49">
-        <v>-0.830113562107197</v>
+        <v>-1.17278001103083</v>
       </c>
       <c r="G49">
-        <v>-4.941818004415398</v>
+        <v>-4.908351699558906</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.810633896411816</v>
       </c>
       <c r="E50">
-        <v>-13.73139945935593</v>
+        <v>-10.74093107891065</v>
       </c>
       <c r="F50">
-        <v>-1.018183390683378</v>
+        <v>-1.42704874687238</v>
       </c>
       <c r="G50">
-        <v>-5.309189242908322</v>
+        <v>-3.724222528890231</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.919477109027096</v>
       </c>
       <c r="E51">
-        <v>-11.84030418527878</v>
+        <v>-12.65380378449069</v>
       </c>
       <c r="F51">
-        <v>-0.974987019986809</v>
+        <v>-1.797342153637896</v>
       </c>
       <c r="G51">
-        <v>-4.669717645451621</v>
+        <v>-4.462580121604962</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.076813361326867</v>
       </c>
       <c r="E52">
-        <v>-12.36025904236548</v>
+        <v>-12.01105935468601</v>
       </c>
       <c r="F52">
-        <v>-1.31477904267392</v>
+        <v>-1.332446074013604</v>
       </c>
       <c r="G52">
-        <v>-4.595750126467685</v>
+        <v>-4.06431156159402</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.279802728593448</v>
       </c>
       <c r="E53">
-        <v>-11.29076933597397</v>
+        <v>-11.4527890790204</v>
       </c>
       <c r="F53">
-        <v>-1.138522868373959</v>
+        <v>-1.172296980726621</v>
       </c>
       <c r="G53">
-        <v>-4.746422985596534</v>
+        <v>-3.442011763849519</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.530712753717084</v>
       </c>
       <c r="E54">
-        <v>-11.17726313497172</v>
+        <v>-10.58331301259968</v>
       </c>
       <c r="F54">
-        <v>-1.008500612716381</v>
+        <v>-1.495368236358522</v>
       </c>
       <c r="G54">
-        <v>-4.859620469220834</v>
+        <v>-5.192105178820918</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.834148460470239</v>
       </c>
       <c r="E55">
-        <v>-11.20564308157779</v>
+        <v>-9.628909944639107</v>
       </c>
       <c r="F55">
-        <v>-1.092174131052709</v>
+        <v>-1.692827857307343</v>
       </c>
       <c r="G55">
-        <v>-4.626458746889965</v>
+        <v>-3.737752728509232</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.184539815673547</v>
       </c>
       <c r="E56">
-        <v>-11.88857318972654</v>
+        <v>-9.821868222105939</v>
       </c>
       <c r="F56">
-        <v>-1.428894556116824</v>
+        <v>-1.384920585815775</v>
       </c>
       <c r="G56">
-        <v>-4.92291478938616</v>
+        <v>-3.576482813109175</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.58080860720226</v>
       </c>
       <c r="E57">
-        <v>-10.41239934660219</v>
+        <v>-10.13087317449333</v>
       </c>
       <c r="F57">
-        <v>-1.227042526811532</v>
+        <v>-1.979542768091459</v>
       </c>
       <c r="G57">
-        <v>-5.231027262726129</v>
+        <v>-3.860434925103544</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.010773275677989</v>
       </c>
       <c r="E58">
-        <v>-10.93338669576264</v>
+        <v>-9.895238557978216</v>
       </c>
       <c r="F58">
-        <v>-1.173559986194184</v>
+        <v>-1.578344924092057</v>
       </c>
       <c r="G58">
-        <v>-5.433963704283453</v>
+        <v>-4.616229161173616</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.464666711058912</v>
       </c>
       <c r="E59">
-        <v>-9.833302618975308</v>
+        <v>-7.780386854708066</v>
       </c>
       <c r="F59">
-        <v>-1.100370601018066</v>
+        <v>-1.733695388455258</v>
       </c>
       <c r="G59">
-        <v>-4.694324930445024</v>
+        <v>-4.297085950096795</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.935551860501616</v>
       </c>
       <c r="E60">
-        <v>-9.787759755880167</v>
+        <v>-8.133331590391887</v>
       </c>
       <c r="F60">
-        <v>-1.565905705979237</v>
+        <v>-1.402097460174631</v>
       </c>
       <c r="G60">
-        <v>-4.646047244845832</v>
+        <v>-4.406926540544275</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.406448514284438</v>
       </c>
       <c r="E61">
-        <v>-9.524773156358718</v>
+        <v>-8.194008613620662</v>
       </c>
       <c r="F61">
-        <v>-1.098509746567424</v>
+        <v>-1.458699109592437</v>
       </c>
       <c r="G61">
-        <v>-5.516962391498521</v>
+        <v>-4.909536874861965</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.868142436144639</v>
       </c>
       <c r="E62">
-        <v>-9.831957662195029</v>
+        <v>-8.258027650667097</v>
       </c>
       <c r="F62">
-        <v>-1.195072255496556</v>
+        <v>-1.446034213386668</v>
       </c>
       <c r="G62">
-        <v>-5.736405213114651</v>
+        <v>-4.98237549781701</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.303130538563227</v>
       </c>
       <c r="E63">
-        <v>-9.52665700154591</v>
+        <v>-8.076707551399975</v>
       </c>
       <c r="F63">
-        <v>-1.321946895647199</v>
+        <v>-2.014720835738157</v>
       </c>
       <c r="G63">
-        <v>-5.756794863091022</v>
+        <v>-3.969053924247032</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.694176577512246</v>
       </c>
       <c r="E64">
-        <v>-9.07589722729641</v>
+        <v>-7.491497383862743</v>
       </c>
       <c r="F64">
-        <v>-0.9241247208065557</v>
+        <v>-1.656801715142927</v>
       </c>
       <c r="G64">
-        <v>-5.578210794520577</v>
+        <v>-5.315621632891126</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.029053661056291</v>
       </c>
       <c r="E65">
-        <v>-8.483907934169695</v>
+        <v>-7.718283362166875</v>
       </c>
       <c r="F65">
-        <v>-1.33538543219266</v>
+        <v>-1.812125256505566</v>
       </c>
       <c r="G65">
-        <v>-5.95225940336621</v>
+        <v>-6.034228510918566</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.289099851876971</v>
       </c>
       <c r="E66">
-        <v>-9.533209703435009</v>
+        <v>-8.051171486470723</v>
       </c>
       <c r="F66">
-        <v>-1.260403291920264</v>
+        <v>-1.877001769331543</v>
       </c>
       <c r="G66">
-        <v>-6.286932383567753</v>
+        <v>-4.596369198483528</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.469547659640625</v>
       </c>
       <c r="E67">
-        <v>-9.300681620089151</v>
+        <v>-6.902791234391589</v>
       </c>
       <c r="F67">
-        <v>-1.39256196685777</v>
+        <v>-1.52776135715292</v>
       </c>
       <c r="G67">
-        <v>-5.833536619236868</v>
+        <v>-5.740781754317568</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.565895238692284</v>
       </c>
       <c r="E68">
-        <v>-8.945155654220958</v>
+        <v>-6.688589885354774</v>
       </c>
       <c r="F68">
-        <v>-1.3700907636236</v>
+        <v>-1.714724175294209</v>
       </c>
       <c r="G68">
-        <v>-5.966315979725956</v>
+        <v>-5.010839568363664</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.577788520739325</v>
       </c>
       <c r="E69">
-        <v>-9.020310208852257</v>
+        <v>-7.75849168288098</v>
       </c>
       <c r="F69">
-        <v>-1.328459094371486</v>
+        <v>-1.914353473347182</v>
       </c>
       <c r="G69">
-        <v>-6.173423708662762</v>
+        <v>-5.781008193165252</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.514651166980251</v>
       </c>
       <c r="E70">
-        <v>-7.930800118872837</v>
+        <v>-7.213634747226098</v>
       </c>
       <c r="F70">
-        <v>-1.534089054138059</v>
+        <v>-1.606947444777851</v>
       </c>
       <c r="G70">
-        <v>-6.437784012155723</v>
+        <v>-5.402146051105517</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.380898946624515</v>
       </c>
       <c r="E71">
-        <v>-9.310399725309612</v>
+        <v>-7.338946679966352</v>
       </c>
       <c r="F71">
-        <v>-1.297734407759003</v>
+        <v>-1.736517552396571</v>
       </c>
       <c r="G71">
-        <v>-6.262523731306707</v>
+        <v>-6.087544846828528</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.194183187759196</v>
       </c>
       <c r="E72">
-        <v>-9.87513213338416</v>
+        <v>-7.542655554727395</v>
       </c>
       <c r="F72">
-        <v>-1.554411168444978</v>
+        <v>-2.165457172916726</v>
       </c>
       <c r="G72">
-        <v>-6.328992864644193</v>
+        <v>-5.344622011815142</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.968766100690954</v>
       </c>
       <c r="E73">
-        <v>-8.954692620481113</v>
+        <v>-6.496138796976799</v>
       </c>
       <c r="F73">
-        <v>-1.620590279386404</v>
+        <v>-2.123720187221235</v>
       </c>
       <c r="G73">
-        <v>-6.190151895272699</v>
+        <v>-6.21549412137582</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.71623105759165</v>
       </c>
       <c r="E74">
-        <v>-8.009233288685687</v>
+        <v>-7.974585934053001</v>
       </c>
       <c r="F74">
-        <v>-1.532474465957268</v>
+        <v>-1.789775998626885</v>
       </c>
       <c r="G74">
-        <v>-6.086511956620275</v>
+        <v>-5.207297272300633</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.454520593415229</v>
       </c>
       <c r="E75">
-        <v>-8.985531528473347</v>
+        <v>-9.089921911298164</v>
       </c>
       <c r="F75">
-        <v>-1.721334563785253</v>
+        <v>-2.157562398928261</v>
       </c>
       <c r="G75">
-        <v>-6.009002153909319</v>
+        <v>-6.098896707482689</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.188280583083144</v>
       </c>
       <c r="E76">
-        <v>-9.767277467943474</v>
+        <v>-8.795217879826993</v>
       </c>
       <c r="F76">
-        <v>-1.953521688047831</v>
+        <v>-2.638078569996532</v>
       </c>
       <c r="G76">
-        <v>-6.282800822734742</v>
+        <v>-6.207767308087161</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.929139781627469</v>
       </c>
       <c r="E77">
-        <v>-10.43040455925668</v>
+        <v>-9.553569722573494</v>
       </c>
       <c r="F77">
-        <v>-1.770256031366136</v>
+        <v>-2.241873358895553</v>
       </c>
       <c r="G77">
-        <v>-6.51029489110238</v>
+        <v>-5.833884226518491</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.682508153383663</v>
       </c>
       <c r="E78">
-        <v>-10.89576413370691</v>
+        <v>-8.563192457095987</v>
       </c>
       <c r="F78">
-        <v>-1.796975525718472</v>
+        <v>-2.136924335291211</v>
       </c>
       <c r="G78">
-        <v>-6.225740259819864</v>
+        <v>-5.593664421097895</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.447976013383408</v>
       </c>
       <c r="E79">
-        <v>-11.90436850706529</v>
+        <v>-8.14492901232553</v>
       </c>
       <c r="F79">
-        <v>-2.036950523820223</v>
+        <v>-2.409045396064552</v>
       </c>
       <c r="G79">
-        <v>-6.87295522329292</v>
+        <v>-5.872786447150466</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.232913459674791</v>
       </c>
       <c r="E80">
-        <v>-12.36188929300824</v>
+        <v>-10.13933689241367</v>
       </c>
       <c r="F80">
-        <v>-2.190696694091085</v>
+        <v>-2.667484029581454</v>
       </c>
       <c r="G80">
-        <v>-6.729264304706394</v>
+        <v>-5.87258781441811</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.032324033284119</v>
       </c>
       <c r="E81">
-        <v>-12.17661130745842</v>
+        <v>-10.85838158077359</v>
       </c>
       <c r="F81">
-        <v>-2.289085215940718</v>
+        <v>-2.609103086567652</v>
       </c>
       <c r="G81">
-        <v>-6.218089589078609</v>
+        <v>-6.187751749756727</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.849180598782727</v>
       </c>
       <c r="E82">
-        <v>-12.97650284227728</v>
+        <v>-11.38902816499241</v>
       </c>
       <c r="F82">
-        <v>-2.274471569606001</v>
+        <v>-2.597198369201294</v>
       </c>
       <c r="G82">
-        <v>-6.974128805518587</v>
+        <v>-5.576029145010198</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.683401436626216</v>
       </c>
       <c r="E83">
-        <v>-14.19844815461102</v>
+        <v>-12.50575891223193</v>
       </c>
       <c r="F83">
-        <v>-2.224235626115304</v>
+        <v>-3.058093215830228</v>
       </c>
       <c r="G83">
-        <v>-6.83884336205627</v>
+        <v>-5.740063365935545</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.529936054013796</v>
       </c>
       <c r="E84">
-        <v>-14.9581449541378</v>
+        <v>-12.96180341564838</v>
       </c>
       <c r="F84">
-        <v>-2.44893261325081</v>
+        <v>-2.705800210499596</v>
       </c>
       <c r="G84">
-        <v>-6.397792622041327</v>
+        <v>-5.628305969620829</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.394354734220255</v>
       </c>
       <c r="E85">
-        <v>-16.34508974541501</v>
+        <v>-13.88369204023388</v>
       </c>
       <c r="F85">
-        <v>-2.594123604166468</v>
+        <v>-2.832155395109974</v>
       </c>
       <c r="G85">
-        <v>-7.011418790472938</v>
+        <v>-5.285800238673371</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.272834357856049</v>
       </c>
       <c r="E86">
-        <v>-16.63861637364419</v>
+        <v>-15.60692583979471</v>
       </c>
       <c r="F86">
-        <v>-2.715009460397876</v>
+        <v>-3.052033165144798</v>
       </c>
       <c r="G86">
-        <v>-5.912085933247155</v>
+        <v>-5.782971346670039</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.170037739022406</v>
       </c>
       <c r="E87">
-        <v>-17.96403278857919</v>
+        <v>-16.54697364515097</v>
       </c>
       <c r="F87">
-        <v>-3.0975100723596</v>
+        <v>-3.185540365669302</v>
       </c>
       <c r="G87">
-        <v>-6.726615868274977</v>
+        <v>-5.330131753989751</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.090948212727848</v>
       </c>
       <c r="E88">
-        <v>-19.36725744391398</v>
+        <v>-18.91601765141967</v>
       </c>
       <c r="F88">
-        <v>-2.840053336510271</v>
+        <v>-3.048864169608005</v>
       </c>
       <c r="G88">
-        <v>-6.304316058194466</v>
+        <v>-4.842766481880404</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.035470446177946</v>
       </c>
       <c r="E89">
-        <v>-20.76957640444724</v>
+        <v>-18.06221463353949</v>
       </c>
       <c r="F89">
-        <v>-3.0290923931067</v>
+        <v>-3.493057253652714</v>
       </c>
       <c r="G89">
-        <v>-6.571334729755463</v>
+        <v>-4.673839274648014</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.0154832174699</v>
       </c>
       <c r="E90">
-        <v>-22.56250341898611</v>
+        <v>-19.94981392568272</v>
       </c>
       <c r="F90">
-        <v>-2.86561197442659</v>
+        <v>-3.299969452883464</v>
       </c>
       <c r="G90">
-        <v>-6.554424463140865</v>
+        <v>-5.099188097170194</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.031706333873509</v>
       </c>
       <c r="E91">
-        <v>-23.97981615695876</v>
+        <v>-22.390045543352</v>
       </c>
       <c r="F91">
-        <v>-2.951396572748199</v>
+        <v>-3.492061102631903</v>
       </c>
       <c r="G91">
-        <v>-6.296685250726446</v>
+        <v>-4.927407199682951</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.09048343114045</v>
       </c>
       <c r="E92">
-        <v>-25.90919062182275</v>
+        <v>-24.02320346642625</v>
       </c>
       <c r="F92">
-        <v>-3.162042129148969</v>
+        <v>-3.554026763985302</v>
       </c>
       <c r="G92">
-        <v>-6.450082688834115</v>
+        <v>-6.21222661292856</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.19761184854855</v>
       </c>
       <c r="E93">
-        <v>-28.67084879608246</v>
+        <v>-27.71562154585249</v>
       </c>
       <c r="F93">
-        <v>-3.081680931734783</v>
+        <v>-3.53900135411257</v>
       </c>
       <c r="G93">
-        <v>-7.171477046205621</v>
+        <v>-5.672677211483681</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.34984202627233</v>
       </c>
       <c r="E94">
-        <v>-30.67798168813215</v>
+        <v>-28.47213482815188</v>
       </c>
       <c r="F94">
-        <v>-3.04299337177947</v>
+        <v>-3.462824307726975</v>
       </c>
       <c r="G94">
-        <v>-6.768302257705479</v>
+        <v>-5.387367775818211</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.554223266452873</v>
       </c>
       <c r="E95">
-        <v>-32.54393487451872</v>
+        <v>-31.29556818058723</v>
       </c>
       <c r="F95">
-        <v>-2.843813846206482</v>
+        <v>-3.946886396339916</v>
       </c>
       <c r="G95">
-        <v>-7.496466680704795</v>
+        <v>-6.520527787364268</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.814295188402301</v>
       </c>
       <c r="E96">
-        <v>-35.25948865490634</v>
+        <v>-33.92308616202873</v>
       </c>
       <c r="F96">
-        <v>-2.684040091221458</v>
+        <v>-3.970166081443918</v>
       </c>
       <c r="G96">
-        <v>-6.984265695959836</v>
+        <v>-6.040571516171809</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.124370532383558</v>
       </c>
       <c r="E97">
-        <v>-37.58698844062867</v>
+        <v>-36.21755299410211</v>
       </c>
       <c r="F97">
-        <v>-2.894355444938859</v>
+        <v>-3.703385277017439</v>
       </c>
       <c r="G97">
-        <v>-7.082191633011478</v>
+        <v>-7.284482518188644</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.509476471472346</v>
       </c>
       <c r="E98">
-        <v>-41.03192315129873</v>
+        <v>-38.94220674300815</v>
       </c>
       <c r="F98">
-        <v>-2.723703214020681</v>
+        <v>-3.773484851952535</v>
       </c>
       <c r="G98">
-        <v>-7.292490727848141</v>
+        <v>-6.533339598601247</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.939711231103711</v>
       </c>
       <c r="E99">
-        <v>-42.76027412648822</v>
+        <v>-40.16772954980795</v>
       </c>
       <c r="F99">
-        <v>-3.012973434299358</v>
+        <v>-3.781958470453094</v>
       </c>
       <c r="G99">
-        <v>-8.153504032792869</v>
+        <v>-8.095152357117675</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.470451584080937</v>
       </c>
       <c r="E100">
-        <v>-45.25220733190307</v>
+        <v>-44.84177814716588</v>
       </c>
       <c r="F100">
-        <v>-2.390810606154183</v>
+        <v>-3.479788965493162</v>
       </c>
       <c r="G100">
-        <v>-8.08372766446165</v>
+        <v>-7.80978002108696</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.028498434611926</v>
       </c>
       <c r="E101">
-        <v>-47.78001284416968</v>
+        <v>-46.82479691512473</v>
       </c>
       <c r="F101">
-        <v>-2.647488950546073</v>
+        <v>-3.377620929476333</v>
       </c>
       <c r="G101">
-        <v>-9.420390220852246</v>
+        <v>-8.106586981410318</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.733865329027229</v>
       </c>
       <c r="E102">
-        <v>-50.58711651933337</v>
+        <v>-48.94821762333589</v>
       </c>
       <c r="F102">
-        <v>-2.393803810334363</v>
+        <v>-3.411597756186171</v>
       </c>
       <c r="G102">
-        <v>-9.40996862349462</v>
+        <v>-7.759588840166069</v>
       </c>
     </row>
   </sheetData>
